--- a/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Zoubiria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405D1936-BDED-4763-8A74-CC2875B64F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{244934D4-735F-4474-82A3-954D431FFE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,13 +179,13 @@
     <t>2025177220</t>
   </si>
   <si>
-    <t>Atari lakhdar</t>
-  </si>
-  <si>
     <t>131957</t>
   </si>
   <si>
     <t>2025177680</t>
+  </si>
+  <si>
+    <t>Amari lakhdar</t>
   </si>
 </sst>
 </file>
@@ -1798,7 +1798,7 @@
         <v>25</v>
       </c>
       <c r="E7" s="12">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="F7" s="19" t="s">
         <v>22</v>
@@ -1807,7 +1807,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -1819,16 +1819,16 @@
         <v>2</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" s="12">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="F8" s="19" t="s">
         <v>22</v>

--- a/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Zoubiria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{244934D4-735F-4474-82A3-954D431FFE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2AECA19-B412-4F67-9CED-E073C41F32BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2026" sheetId="12" r:id="rId1"/>
-    <sheet name="DECEMBRE 2026" sheetId="13" r:id="rId2"/>
+    <sheet name="FEVRIER 2026" sheetId="13" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'DECEMBRE 2026'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'FEVRIER 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'JANVIER 2026'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -149,8 +149,20 @@
     <t>Elimination Forfait</t>
   </si>
   <si>
+    <t>2025177220</t>
+  </si>
+  <si>
+    <t>131957</t>
+  </si>
+  <si>
+    <t>2025177680</t>
+  </si>
+  <si>
+    <t>Amari lakhdar</t>
+  </si>
+  <si>
     <r>
-      <t>Mois de DECEMBRE</t>
+      <t>Mois de FEVRIER</t>
     </r>
     <r>
       <rPr>
@@ -173,19 +185,10 @@
     </r>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>2025177220</t>
-  </si>
-  <si>
-    <t>131957</t>
-  </si>
-  <si>
-    <t>2025177680</t>
-  </si>
-  <si>
-    <t>Amari lakhdar</t>
+    <t>132293</t>
+  </si>
+  <si>
+    <t>NB</t>
   </si>
 </sst>
 </file>
@@ -1692,7 +1695,7 @@
       <c r="J2" s="23"/>
       <c r="K2" s="16">
         <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1714,7 +1717,7 @@
       <c r="J3" s="23"/>
       <c r="K3" s="16">
         <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -1739,7 +1742,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
@@ -1789,25 +1792,25 @@
         <v>1</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E7" s="12">
         <v>46062</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G7" s="15">
         <v>1</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -1819,13 +1822,13 @@
         <v>2</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E8" s="12">
         <v>46062</v>

--- a/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Zoubiria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2AECA19-B412-4F67-9CED-E073C41F32BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3C8470-FCC5-4ECD-BD7E-F067A8EC4E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2026" sheetId="12" r:id="rId1"/>
     <sheet name="FEVRIER 2026" sheetId="13" r:id="rId2"/>
+    <sheet name="MARS 2026" sheetId="14" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'FEVRIER 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'JANVIER 2026'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'MARS 2026'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="31">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -189,6 +191,30 @@
   </si>
   <si>
     <t>NB</t>
+  </si>
+  <si>
+    <r>
+      <t>Mois de MARS</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -554,6 +580,61 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19052</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Connecteur droit 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46FDAACF-DF97-4249-B82D-0495A45E187C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="609602" y="1352550"/>
+          <a:ext cx="4076698" cy="7562850"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -2457,4 +2538,796 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D131A12-1E48-4B0E-8755-3544D84B7B06}">
+  <dimension ref="A1:K46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="6"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="26"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="23"/>
+      <c r="K2" s="16">
+        <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="26"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="23"/>
+      <c r="K3" s="16">
+        <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="23"/>
+      <c r="K4" s="16">
+        <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="23"/>
+      <c r="K5" s="18">
+        <f>SUM(K2:K4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14">
+        <v>1</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="15">
+        <v>1</v>
+      </c>
+      <c r="H7" s="20"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14">
+        <f t="shared" ref="A8:A46" si="0">+A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="15">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="15">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="15">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="15">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="15">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="15">
+        <v>1</v>
+      </c>
+      <c r="H13" s="20"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="15">
+        <v>1</v>
+      </c>
+      <c r="H14" s="11"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="15">
+        <v>1</v>
+      </c>
+      <c r="H16" s="20"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="15">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="15">
+        <v>1</v>
+      </c>
+      <c r="H18" s="20"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="15">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="15">
+        <v>1</v>
+      </c>
+      <c r="H20" s="11"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="15">
+        <v>1</v>
+      </c>
+      <c r="H21" s="20"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="20"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="15">
+        <v>1</v>
+      </c>
+      <c r="H24" s="11"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="14">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="15">
+        <v>1</v>
+      </c>
+      <c r="H25" s="11"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="15">
+        <v>1</v>
+      </c>
+      <c r="H26" s="11"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="14">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="11"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="15">
+        <v>1</v>
+      </c>
+      <c r="H28" s="20"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="15">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="15">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="15">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="15">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="9"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="15">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B35" s="9"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="15">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="15">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="14">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="19"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="14">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B38" s="9"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="19"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="14">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="19"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="14">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="19"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="14">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="19"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="14">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="9"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="19"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="14">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="19"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="14">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="19"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="14">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B45" s="9"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="19"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="14">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Zoubiria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3C8470-FCC5-4ECD-BD7E-F067A8EC4E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE9F1EC-3C1C-4AE9-8055-F5EB15BB9C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2026" sheetId="12" r:id="rId1"/>
     <sheet name="FEVRIER 2026" sheetId="13" r:id="rId2"/>
     <sheet name="MARS 2026" sheetId="14" r:id="rId3"/>
+    <sheet name="AVRIL 2026" sheetId="15" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'AVRIL 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'FEVRIER 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'JANVIER 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'MARS 2026'!$1:$6</definedName>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="39">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -215,6 +217,51 @@
       </rPr>
       <t>2026</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>Mois de AVRIL</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>2025177477</t>
+  </si>
+  <si>
+    <t>Hosni mhamed</t>
+  </si>
+  <si>
+    <t>NB(157/2026)</t>
+  </si>
+  <si>
+    <t>2025177480</t>
+  </si>
+  <si>
+    <t>NB(158/2026)</t>
+  </si>
+  <si>
+    <t>Benmoussa aek</t>
   </si>
 </sst>
 </file>
@@ -635,6 +682,61 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19052</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1162050</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Connecteur droit 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EF2AE9C-ECFB-4625-91AF-534FA0CA0797}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="609602" y="1724025"/>
+          <a:ext cx="4057648" cy="7191375"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -3330,4 +3432,820 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78793CFD-16FA-4457-9C1D-128F252DF9C3}">
+  <dimension ref="A1:K46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="6"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="26"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="23"/>
+      <c r="K2" s="16">
+        <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="26"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="23"/>
+      <c r="K3" s="16">
+        <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="23"/>
+      <c r="K4" s="16">
+        <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="23"/>
+      <c r="K5" s="18">
+        <f>SUM(K2:K4)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14">
+        <v>1</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="12">
+        <v>46134</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="15">
+        <v>1</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14">
+        <f t="shared" ref="A8:A46" si="0">+A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="12">
+        <v>46134</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="15">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="15">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="15">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="15">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="15">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="15">
+        <v>1</v>
+      </c>
+      <c r="H13" s="20"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="15">
+        <v>1</v>
+      </c>
+      <c r="H14" s="11"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="15">
+        <v>1</v>
+      </c>
+      <c r="H16" s="20"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="15">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="15">
+        <v>1</v>
+      </c>
+      <c r="H18" s="20"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="15">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="15">
+        <v>1</v>
+      </c>
+      <c r="H20" s="11"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="15">
+        <v>1</v>
+      </c>
+      <c r="H21" s="20"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="20"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="15">
+        <v>1</v>
+      </c>
+      <c r="H24" s="11"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="14">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="15">
+        <v>1</v>
+      </c>
+      <c r="H25" s="11"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="15">
+        <v>1</v>
+      </c>
+      <c r="H26" s="11"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="14">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="11"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="15">
+        <v>1</v>
+      </c>
+      <c r="H28" s="20"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="15">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="15">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="15">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="15">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="9"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="15">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B35" s="9"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="15">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="15">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="14">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="19"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="14">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B38" s="9"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="19"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="14">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="19"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="14">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="19"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="14">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="19"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="14">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="9"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="19"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="14">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="19"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="14">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="19"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="14">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B45" s="9"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="19"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="14">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
@@ -1,27 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Zoubiria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE9F1EC-3C1C-4AE9-8055-F5EB15BB9C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E919FF-ADD2-44A9-BDF0-CD07A7384AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2026" sheetId="12" r:id="rId1"/>
     <sheet name="FEVRIER 2026" sheetId="13" r:id="rId2"/>
     <sheet name="MARS 2026" sheetId="14" r:id="rId3"/>
     <sheet name="AVRIL 2026" sheetId="15" r:id="rId4"/>
+    <sheet name="MAI 2026" sheetId="16" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'AVRIL 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'FEVRIER 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'JANVIER 2026'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'MAI 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'MARS 2026'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="40">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -262,6 +264,30 @@
   </si>
   <si>
     <t>Benmoussa aek</t>
+  </si>
+  <si>
+    <r>
+      <t>Mois de MAI</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -737,6 +763,61 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19052</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1162050</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Connecteur droit 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA4504FE-58A9-40E0-AB4B-DCBF68A206CC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="609602" y="1724025"/>
+          <a:ext cx="4057648" cy="7191375"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -4248,4 +4329,806 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F538D8A8-A20F-4ADD-84DE-C29A53D550E7}">
+  <dimension ref="A1:K46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="6"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="26"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="23"/>
+      <c r="K2" s="16">
+        <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="26"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="23"/>
+      <c r="K3" s="16">
+        <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="23"/>
+      <c r="K4" s="16">
+        <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="23"/>
+      <c r="K5" s="18">
+        <f>SUM(K2:K4)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10">
+        <v>131332</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="10">
+        <v>2025177164</v>
+      </c>
+      <c r="E7" s="12">
+        <v>46146</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="15">
+        <v>1</v>
+      </c>
+      <c r="H7" s="20"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14">
+        <f t="shared" ref="A8:A46" si="0">+A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="15">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="15">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="15">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="15">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="15">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="15">
+        <v>1</v>
+      </c>
+      <c r="H13" s="20"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="15">
+        <v>1</v>
+      </c>
+      <c r="H14" s="11"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="15">
+        <v>1</v>
+      </c>
+      <c r="H16" s="20"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="15">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="15">
+        <v>1</v>
+      </c>
+      <c r="H18" s="20"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="15">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="15">
+        <v>1</v>
+      </c>
+      <c r="H20" s="11"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="15">
+        <v>1</v>
+      </c>
+      <c r="H21" s="20"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="20"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="15">
+        <v>1</v>
+      </c>
+      <c r="H24" s="11"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="14">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="15">
+        <v>1</v>
+      </c>
+      <c r="H25" s="11"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="15">
+        <v>1</v>
+      </c>
+      <c r="H26" s="11"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="14">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="11"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="15">
+        <v>1</v>
+      </c>
+      <c r="H28" s="20"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="15">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="15">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="15">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="15">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="9"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="15">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B35" s="9"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="15">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="15">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="14">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="19"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="14">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B38" s="9"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="19"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="14">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="19"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="14">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="19"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="14">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="19"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="14">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="9"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="19"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="14">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="19"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="14">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="19"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="14">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B45" s="9"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="19"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="14">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Zoubiria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E919FF-ADD2-44A9-BDF0-CD07A7384AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE229D4-73AF-4E4E-A82F-98DD0FCF8CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="46">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -288,6 +288,24 @@
       </rPr>
       <t>2026</t>
     </r>
+  </si>
+  <si>
+    <t>2025177177</t>
+  </si>
+  <si>
+    <t>NB(165/2026)</t>
+  </si>
+  <si>
+    <t>Bouketab mahfoud</t>
+  </si>
+  <si>
+    <t>2025177174</t>
+  </si>
+  <si>
+    <t>NB(122/2026)</t>
+  </si>
+  <si>
+    <t>Abrous med</t>
   </si>
 </sst>
 </file>
@@ -769,12 +787,12 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>19052</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1162050</xdr:colOff>
+      <xdr:colOff>1171575</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
@@ -791,8 +809,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="609602" y="1724025"/>
-          <a:ext cx="4057648" cy="7191375"/>
+          <a:off x="609602" y="1933575"/>
+          <a:ext cx="4067173" cy="6981825"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -4403,7 +4421,7 @@
       <c r="J3" s="23"/>
       <c r="K3" s="16">
         <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -4443,7 +4461,7 @@
       <c r="J5" s="23"/>
       <c r="K5" s="18">
         <f>SUM(K2:K4)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4505,15 +4523,27 @@
         <f t="shared" ref="A8:A46" si="0">+A7+1</f>
         <v>2</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="19"/>
+      <c r="B8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="12">
+        <v>46152</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>44</v>
+      </c>
       <c r="G8" s="15">
         <v>1</v>
       </c>
-      <c r="H8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="1"/>
@@ -4523,15 +4553,27 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="19"/>
+      <c r="B9" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="12">
+        <v>46152</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>41</v>
+      </c>
       <c r="G9" s="15">
         <v>1</v>
       </c>
-      <c r="H9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="1"/>
@@ -5110,6 +5152,10 @@
       <c r="F46" s="19"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H9">
+    <sortCondition ref="E7:E9"/>
+    <sortCondition ref="D7:D9"/>
+  </sortState>
   <mergeCells count="11">
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="I4:J4"/>

--- a/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Zoubiria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE229D4-73AF-4E4E-A82F-98DD0FCF8CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0322EF0-DDAC-4779-A17E-DE883CDF2947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2026" sheetId="12" r:id="rId1"/>
@@ -18,11 +18,13 @@
     <sheet name="MARS 2026" sheetId="14" r:id="rId3"/>
     <sheet name="AVRIL 2026" sheetId="15" r:id="rId4"/>
     <sheet name="MAI 2026" sheetId="16" r:id="rId5"/>
+    <sheet name="JUIN 2026" sheetId="17" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'AVRIL 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'FEVRIER 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'JANVIER 2026'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'JUIN 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'MAI 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'MARS 2026'!$1:$6</definedName>
   </definedNames>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="47">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -306,6 +308,30 @@
   </si>
   <si>
     <t>Abrous med</t>
+  </si>
+  <si>
+    <r>
+      <t>Mois de JUIN</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -836,6 +862,61 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19052</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1162050</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Connecteur droit 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1E5C4DD-013E-490F-9210-63C99AE21262}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="609602" y="1362075"/>
+          <a:ext cx="4057648" cy="7553325"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -5177,4 +5258,796 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8522A7C-940D-441D-B2FE-44C611D514ED}">
+  <dimension ref="A1:K46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="6"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="26"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="23"/>
+      <c r="K2" s="16">
+        <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="26"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="23"/>
+      <c r="K3" s="16">
+        <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="23"/>
+      <c r="K4" s="16">
+        <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="23"/>
+      <c r="K5" s="18">
+        <f>SUM(K2:K4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="15">
+        <v>1</v>
+      </c>
+      <c r="H7" s="20"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14">
+        <f t="shared" ref="A8:A46" si="0">+A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="15">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="15">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="15">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="15">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="15">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="15">
+        <v>1</v>
+      </c>
+      <c r="H13" s="20"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="15">
+        <v>1</v>
+      </c>
+      <c r="H14" s="11"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="15">
+        <v>1</v>
+      </c>
+      <c r="H16" s="20"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="15">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="15">
+        <v>1</v>
+      </c>
+      <c r="H18" s="20"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="15">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="15">
+        <v>1</v>
+      </c>
+      <c r="H20" s="11"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="15">
+        <v>1</v>
+      </c>
+      <c r="H21" s="20"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="20"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="15">
+        <v>1</v>
+      </c>
+      <c r="H24" s="11"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="14">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="15">
+        <v>1</v>
+      </c>
+      <c r="H25" s="11"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="15">
+        <v>1</v>
+      </c>
+      <c r="H26" s="11"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="14">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="11"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="15">
+        <v>1</v>
+      </c>
+      <c r="H28" s="20"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="15">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="15">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="15">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="15">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="9"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="15">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B35" s="9"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="15">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="15">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="14">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="19"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="14">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B38" s="9"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="19"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="14">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="19"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="14">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="19"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="14">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="19"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="14">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="9"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="19"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="14">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="19"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="14">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="19"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="14">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B45" s="9"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="19"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="14">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Zoubiria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0322EF0-DDAC-4779-A17E-DE883CDF2947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90B2098-DF38-495F-8DBE-6B65B1B8FF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2026" sheetId="12" r:id="rId1"/>
@@ -19,11 +19,15 @@
     <sheet name="AVRIL 2026" sheetId="15" r:id="rId4"/>
     <sheet name="MAI 2026" sheetId="16" r:id="rId5"/>
     <sheet name="JUIN 2026" sheetId="17" r:id="rId6"/>
+    <sheet name="JUILLET 2026" sheetId="18" r:id="rId7"/>
+    <sheet name="AOUT 2026" sheetId="19" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'AOUT 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'AVRIL 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'FEVRIER 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'JANVIER 2026'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'JUILLET 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'JUIN 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'MAI 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'MARS 2026'!$1:$6</definedName>
@@ -46,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="132">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -333,6 +337,283 @@
       <t>2026</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mois de JUILLET </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mois de AOUT </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
+  <si>
+    <t>20/27</t>
+  </si>
+  <si>
+    <t>Houti med</t>
+  </si>
+  <si>
+    <t>NB(271/2026)</t>
+  </si>
+  <si>
+    <t>NB(259/2026)</t>
+  </si>
+  <si>
+    <t>Benzaidoun aissa</t>
+  </si>
+  <si>
+    <t>Ammad daoud</t>
+  </si>
+  <si>
+    <t>NB(254/2026)</t>
+  </si>
+  <si>
+    <t>Berkani rabah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laref abdelnebi </t>
+  </si>
+  <si>
+    <t>NB(279/2026)</t>
+  </si>
+  <si>
+    <t>NB(640/2024)</t>
+  </si>
+  <si>
+    <t>Chekou aissa</t>
+  </si>
+  <si>
+    <t>NB(098/2026)</t>
+  </si>
+  <si>
+    <t>Barkat benazouz</t>
+  </si>
+  <si>
+    <t>NB(249/2026)</t>
+  </si>
+  <si>
+    <t>Zoulikha hadda</t>
+  </si>
+  <si>
+    <t>NB(281/2026)</t>
+  </si>
+  <si>
+    <t>Soualhi ahmed</t>
+  </si>
+  <si>
+    <t>NB(278/2026)</t>
+  </si>
+  <si>
+    <t>Laref salem</t>
+  </si>
+  <si>
+    <t>NB(287/2026)</t>
+  </si>
+  <si>
+    <t>Laref farid</t>
+  </si>
+  <si>
+    <t>NB(454/2025)</t>
+  </si>
+  <si>
+    <t>Djellal ahmed</t>
+  </si>
+  <si>
+    <t>NB(296/2026)</t>
+  </si>
+  <si>
+    <t>Ammad fatiha</t>
+  </si>
+  <si>
+    <t>NB(260/2026)</t>
+  </si>
+  <si>
+    <t>Laref fatiha</t>
+  </si>
+  <si>
+    <t>NB(290/2026)</t>
+  </si>
+  <si>
+    <t>2023004016</t>
+  </si>
+  <si>
+    <t>NB(167/2025)</t>
+  </si>
+  <si>
+    <t>Boulariah med</t>
+  </si>
+  <si>
+    <t>sidi kouider</t>
+  </si>
+  <si>
+    <t>2023004017</t>
+  </si>
+  <si>
+    <t>Tamen sid ali</t>
+  </si>
+  <si>
+    <t>NB(293/2026)</t>
+  </si>
+  <si>
+    <t>2023004018</t>
+  </si>
+  <si>
+    <t>Lakli boudaya</t>
+  </si>
+  <si>
+    <t>NB(294/2026)</t>
+  </si>
+  <si>
+    <t>2026144293</t>
+  </si>
+  <si>
+    <t>NB(079/2026)</t>
+  </si>
+  <si>
+    <t>Bouras hamida</t>
+  </si>
+  <si>
+    <t>lotis n02</t>
+  </si>
+  <si>
+    <t>2026143581</t>
+  </si>
+  <si>
+    <t>Guettas miloud</t>
+  </si>
+  <si>
+    <t>1er nov</t>
+  </si>
+  <si>
+    <t>NB(554/2025)</t>
+  </si>
+  <si>
+    <t>2026144291</t>
+  </si>
+  <si>
+    <t>tayeb dahache</t>
+  </si>
+  <si>
+    <t>NB(248/2025)</t>
+  </si>
+  <si>
+    <t>2026144296</t>
+  </si>
+  <si>
+    <t>Zenkar yagoub</t>
+  </si>
+  <si>
+    <t>chahid salem</t>
+  </si>
+  <si>
+    <t>NB(426/2025)</t>
+  </si>
+  <si>
+    <t>2026144292</t>
+  </si>
+  <si>
+    <t>Lasheb aek</t>
+  </si>
+  <si>
+    <t>NB(037/2026)</t>
+  </si>
+  <si>
+    <t>2026144298</t>
+  </si>
+  <si>
+    <t>Chemim yahia</t>
+  </si>
+  <si>
+    <t>lotts nabi</t>
+  </si>
+  <si>
+    <t>NB(118/2026)</t>
+  </si>
+  <si>
+    <t>2026144300</t>
+  </si>
+  <si>
+    <t>Chemim ahmed</t>
+  </si>
+  <si>
+    <t>NB(116/2026)</t>
+  </si>
+  <si>
+    <t>2026144299</t>
+  </si>
+  <si>
+    <t>Chemim abdenour</t>
+  </si>
+  <si>
+    <t>NB(117/2026)</t>
+  </si>
+  <si>
+    <t>2023004014</t>
+  </si>
+  <si>
+    <t>Bensadat aissa</t>
+  </si>
+  <si>
+    <t>lotis 80 toubal</t>
+  </si>
+  <si>
+    <t>NB(019/2026)</t>
+  </si>
+  <si>
+    <t>2023004015</t>
+  </si>
+  <si>
+    <t>Bensadat boualem</t>
+  </si>
+  <si>
+    <t>NB(020/2026)</t>
+  </si>
+  <si>
+    <t>2023004013</t>
+  </si>
+  <si>
+    <t>Bensadat aek</t>
+  </si>
+  <si>
+    <t>NB(021/2026)</t>
+  </si>
+  <si>
+    <t>2023004012</t>
+  </si>
+  <si>
+    <t>Bensadat menouar</t>
+  </si>
+  <si>
+    <t>NB(018/2026)</t>
+  </si>
+  <si>
+    <t>2023004011</t>
+  </si>
+  <si>
+    <t>Tarfaoui aek</t>
+  </si>
+  <si>
+    <t>NB(220/2026)</t>
+  </si>
 </sst>
 </file>
 
@@ -341,7 +622,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -418,6 +699,24 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -488,7 +787,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -548,6 +847,9 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -565,6 +867,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -917,6 +1231,116 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19052</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1162050</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Connecteur droit 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26A85F78-CD96-4DB0-A432-3C7718EDA0D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="609602" y="1362075"/>
+          <a:ext cx="4057648" cy="7553325"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19052</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Connecteur droit 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33E9102D-B090-487C-BCF1-34ACE3628D14}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="609602" y="7277100"/>
+          <a:ext cx="4076698" cy="1638300"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -1217,11 +1641,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
       <c r="D1" s="7"/>
       <c r="E1" s="6" t="s">
         <v>1</v>
@@ -1234,84 +1658,84 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="26"/>
+      <c r="F2" s="27"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="23"/>
+      <c r="J2" s="24"/>
       <c r="K2" s="16">
         <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="26"/>
+      <c r="F3" s="27"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="23"/>
+      <c r="J3" s="24"/>
       <c r="K3" s="16">
         <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="23"/>
+      <c r="J4" s="24"/>
       <c r="K4" s="16">
         <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="23"/>
+      <c r="J5" s="24"/>
       <c r="K5" s="18">
         <f>SUM(K2:K4)</f>
         <v>1</v>
@@ -2023,11 +2447,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
       <c r="D1" s="7"/>
       <c r="E1" s="6" t="s">
         <v>1</v>
@@ -2040,84 +2464,84 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="26"/>
+      <c r="F2" s="27"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="23"/>
+      <c r="J2" s="24"/>
       <c r="K2" s="16">
         <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="26"/>
+      <c r="F3" s="27"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="23"/>
+      <c r="J3" s="24"/>
       <c r="K3" s="16">
         <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="23"/>
+      <c r="J4" s="24"/>
       <c r="K4" s="16">
         <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="23"/>
+      <c r="J5" s="24"/>
       <c r="K5" s="18">
         <f>SUM(K2:K4)</f>
         <v>2</v>
@@ -2837,11 +3261,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
       <c r="D1" s="7"/>
       <c r="E1" s="6" t="s">
         <v>1</v>
@@ -2854,84 +3278,84 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="26"/>
+      <c r="F2" s="27"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="23"/>
+      <c r="J2" s="24"/>
       <c r="K2" s="16">
         <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="26"/>
+      <c r="F3" s="27"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="23"/>
+      <c r="J3" s="24"/>
       <c r="K3" s="16">
         <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="23"/>
+      <c r="J4" s="24"/>
       <c r="K4" s="16">
         <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="23"/>
+      <c r="J5" s="24"/>
       <c r="K5" s="18">
         <f>SUM(K2:K4)</f>
         <v>0</v>
@@ -3629,11 +4053,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
       <c r="D1" s="7"/>
       <c r="E1" s="6" t="s">
         <v>1</v>
@@ -3646,84 +4070,84 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="26"/>
+      <c r="F2" s="27"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="23"/>
+      <c r="J2" s="24"/>
       <c r="K2" s="16">
         <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="26"/>
+      <c r="F3" s="27"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="23"/>
+      <c r="J3" s="24"/>
       <c r="K3" s="16">
         <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="23"/>
+      <c r="J4" s="24"/>
       <c r="K4" s="16">
         <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="23"/>
+      <c r="J5" s="24"/>
       <c r="K5" s="18">
         <f>SUM(K2:K4)</f>
         <v>2</v>
@@ -4445,11 +4869,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
       <c r="D1" s="7"/>
       <c r="E1" s="6" t="s">
         <v>1</v>
@@ -4462,84 +4886,84 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="26"/>
+      <c r="F2" s="27"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="23"/>
+      <c r="J2" s="24"/>
       <c r="K2" s="16">
         <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="26"/>
+      <c r="F3" s="27"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="23"/>
+      <c r="J3" s="24"/>
       <c r="K3" s="16">
         <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="23"/>
+      <c r="J4" s="24"/>
       <c r="K4" s="16">
         <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="23"/>
+      <c r="J5" s="24"/>
       <c r="K5" s="18">
         <f>SUM(K2:K4)</f>
         <v>3</v>
@@ -5275,11 +5699,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
       <c r="D1" s="7"/>
       <c r="E1" s="6" t="s">
         <v>1</v>
@@ -5292,84 +5716,84 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="26"/>
+      <c r="F2" s="27"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="23"/>
+      <c r="J2" s="24"/>
       <c r="K2" s="16">
         <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="26"/>
+      <c r="F3" s="27"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="23"/>
+      <c r="J3" s="24"/>
       <c r="K3" s="16">
         <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="23"/>
+      <c r="J4" s="24"/>
       <c r="K4" s="16">
         <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="23"/>
+      <c r="J5" s="24"/>
       <c r="K5" s="18">
         <f>SUM(K2:K4)</f>
         <v>0</v>
@@ -6050,4 +6474,1984 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6BC62E-9CA2-4BB0-8AED-B8DC2DE9F13D}">
+  <dimension ref="A1:K46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="6"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="27"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="24"/>
+      <c r="K2" s="16">
+        <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="27"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="24"/>
+      <c r="K3" s="16">
+        <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="24"/>
+      <c r="K4" s="16">
+        <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="24"/>
+      <c r="K5" s="18">
+        <f>SUM(K2:K4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="15">
+        <v>1</v>
+      </c>
+      <c r="H7" s="20"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14">
+        <f t="shared" ref="A8:A46" si="0">+A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="15">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="15">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="15">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="15">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="15">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="15">
+        <v>1</v>
+      </c>
+      <c r="H13" s="20"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="15">
+        <v>1</v>
+      </c>
+      <c r="H14" s="11"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="15">
+        <v>1</v>
+      </c>
+      <c r="H16" s="20"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="15">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="15">
+        <v>1</v>
+      </c>
+      <c r="H18" s="20"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="15">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="15">
+        <v>1</v>
+      </c>
+      <c r="H20" s="11"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="15">
+        <v>1</v>
+      </c>
+      <c r="H21" s="20"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="20"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="15">
+        <v>1</v>
+      </c>
+      <c r="H24" s="11"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="14">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="15">
+        <v>1</v>
+      </c>
+      <c r="H25" s="11"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="15">
+        <v>1</v>
+      </c>
+      <c r="H26" s="11"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="14">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="11"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="15">
+        <v>1</v>
+      </c>
+      <c r="H28" s="20"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="15">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="15">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="15">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="15">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="9"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="15">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B35" s="9"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="15">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="15">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="14">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="19"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="14">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B38" s="9"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="19"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="14">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="19"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="14">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="19"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="14">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="19"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="14">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="9"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="19"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="14">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="19"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="14">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="19"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="14">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B45" s="9"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="19"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="14">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2A19B1-116B-4C2F-B6D6-D26E17C273E5}">
+  <dimension ref="A1:K46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="6"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="27"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="24"/>
+      <c r="K2" s="16">
+        <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="27"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="24"/>
+      <c r="K3" s="16">
+        <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="24"/>
+      <c r="K4" s="16">
+        <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="24"/>
+      <c r="K5" s="18">
+        <f>SUM(K2:K4)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10">
+        <v>13</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="10">
+        <v>2026003666</v>
+      </c>
+      <c r="E7" s="12">
+        <v>46236</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="15">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14">
+        <f t="shared" ref="A8:A46" si="0">+A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="10">
+        <v>13</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="10">
+        <v>2026003667</v>
+      </c>
+      <c r="E8" s="12">
+        <v>46236</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="15">
+        <v>1</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B9" s="10">
+        <v>13</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="10">
+        <v>2026003668</v>
+      </c>
+      <c r="E9" s="12">
+        <v>46236</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="15">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="10">
+        <v>13</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="10">
+        <v>2026003669</v>
+      </c>
+      <c r="E10" s="12">
+        <v>46236</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="15">
+        <v>1</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="10">
+        <v>13</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="10">
+        <v>2026003671</v>
+      </c>
+      <c r="E11" s="12">
+        <v>46236</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="15">
+        <v>1</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B12" s="10">
+        <v>13</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="10">
+        <v>2026003672</v>
+      </c>
+      <c r="E12" s="12">
+        <v>46236</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="15">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B13" s="10">
+        <v>13</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="10">
+        <v>2026003673</v>
+      </c>
+      <c r="E13" s="12">
+        <v>46236</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="15">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B14" s="10">
+        <v>13</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="10">
+        <v>2026003674</v>
+      </c>
+      <c r="E14" s="12">
+        <v>46236</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="15">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B15" s="10">
+        <v>13</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="10">
+        <v>2026003675</v>
+      </c>
+      <c r="E15" s="12">
+        <v>46236</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B16" s="10">
+        <v>13</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="10">
+        <v>2026003676</v>
+      </c>
+      <c r="E16" s="12">
+        <v>46236</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="15">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B17" s="10">
+        <v>13</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="10">
+        <v>2026003677</v>
+      </c>
+      <c r="E17" s="12">
+        <v>46236</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="15">
+        <v>1</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="10">
+        <v>13</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="10">
+        <v>2026003678</v>
+      </c>
+      <c r="E18" s="12">
+        <v>46236</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18" s="15">
+        <v>1</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B19" s="10">
+        <v>13</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="10">
+        <v>2026003679</v>
+      </c>
+      <c r="E19" s="12">
+        <v>46236</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G19" s="15">
+        <v>1</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B20" s="10">
+        <v>13</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="10">
+        <v>2026003680</v>
+      </c>
+      <c r="E20" s="12">
+        <v>46236</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="15">
+        <v>1</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" s="12">
+        <v>46244</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="G21" s="15">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E22" s="12">
+        <v>46244</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E23" s="12">
+        <v>46244</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E24" s="12">
+        <v>46244</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" s="15">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="14">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E25" s="12">
+        <v>46244</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="G25" s="15">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="12">
+        <v>46244</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="G26" s="15">
+        <v>1</v>
+      </c>
+      <c r="H26" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="14">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="12">
+        <v>46244</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E28" s="12">
+        <v>46244</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="15">
+        <v>1</v>
+      </c>
+      <c r="H28" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="I28" s="21">
+        <v>46208</v>
+      </c>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E29" s="12">
+        <v>46244</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="G29" s="15">
+        <v>1</v>
+      </c>
+      <c r="H29" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="30">
+        <v>46244</v>
+      </c>
+      <c r="F30" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="G30" s="15">
+        <v>1</v>
+      </c>
+      <c r="H30" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" s="12">
+        <v>46244</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E32" s="12">
+        <v>46244</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" s="15">
+        <v>1</v>
+      </c>
+      <c r="H32" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E33" s="12">
+        <v>46244</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="G33" s="15">
+        <v>1</v>
+      </c>
+      <c r="H33" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E34" s="12">
+        <v>46244</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="G34" s="15">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E35" s="12">
+        <v>46244</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="G35" s="15">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E36" s="12">
+        <v>46244</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="G36" s="15">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="14">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="19"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="14">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B38" s="9"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="19"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="14">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="19"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="14">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="19"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="14">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="19"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="14">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="9"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="19"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="14">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="19"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="14">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="19"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="14">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B45" s="9"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="19"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="14">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="19"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I36">
+    <sortCondition ref="E7:E36"/>
+    <sortCondition ref="D7:D36"/>
+  </sortState>
+  <mergeCells count="11">
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <phoneticPr fontId="13" type="noConversion"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Zoubiria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90B2098-DF38-495F-8DBE-6B65B1B8FF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980581EE-C2EC-4807-9756-7781CE3F1335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="125">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -462,9 +462,6 @@
     <t>Boulariah med</t>
   </si>
   <si>
-    <t>sidi kouider</t>
-  </si>
-  <si>
     <t>2023004017</t>
   </si>
   <si>
@@ -492,27 +489,18 @@
     <t>Bouras hamida</t>
   </si>
   <si>
-    <t>lotis n02</t>
-  </si>
-  <si>
     <t>2026143581</t>
   </si>
   <si>
     <t>Guettas miloud</t>
   </si>
   <si>
-    <t>1er nov</t>
-  </si>
-  <si>
     <t>NB(554/2025)</t>
   </si>
   <si>
     <t>2026144291</t>
   </si>
   <si>
-    <t>tayeb dahache</t>
-  </si>
-  <si>
     <t>NB(248/2025)</t>
   </si>
   <si>
@@ -522,9 +510,6 @@
     <t>Zenkar yagoub</t>
   </si>
   <si>
-    <t>chahid salem</t>
-  </si>
-  <si>
     <t>NB(426/2025)</t>
   </si>
   <si>
@@ -543,9 +528,6 @@
     <t>Chemim yahia</t>
   </si>
   <si>
-    <t>lotts nabi</t>
-  </si>
-  <si>
     <t>NB(118/2026)</t>
   </si>
   <si>
@@ -571,9 +553,6 @@
   </si>
   <si>
     <t>Bensadat aissa</t>
-  </si>
-  <si>
-    <t>lotis 80 toubal</t>
   </si>
   <si>
     <t>NB(019/2026)</t>
@@ -850,6 +829,18 @@
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -867,18 +858,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1641,11 +1620,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
       <c r="D1" s="7"/>
       <c r="E1" s="6" t="s">
         <v>1</v>
@@ -1658,84 +1637,84 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="27"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="24"/>
+      <c r="J2" s="28"/>
       <c r="K2" s="16">
         <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="27"/>
+      <c r="F3" s="31"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="24"/>
+      <c r="J3" s="28"/>
       <c r="K3" s="16">
         <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="24"/>
+      <c r="J4" s="28"/>
       <c r="K4" s="16">
         <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="24"/>
+      <c r="J5" s="28"/>
       <c r="K5" s="18">
         <f>SUM(K2:K4)</f>
         <v>1</v>
@@ -2447,11 +2426,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
       <c r="D1" s="7"/>
       <c r="E1" s="6" t="s">
         <v>1</v>
@@ -2464,84 +2443,84 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="27"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="24"/>
+      <c r="J2" s="28"/>
       <c r="K2" s="16">
         <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="27"/>
+      <c r="F3" s="31"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="24"/>
+      <c r="J3" s="28"/>
       <c r="K3" s="16">
         <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="24"/>
+      <c r="J4" s="28"/>
       <c r="K4" s="16">
         <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="24"/>
+      <c r="J5" s="28"/>
       <c r="K5" s="18">
         <f>SUM(K2:K4)</f>
         <v>2</v>
@@ -3261,11 +3240,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
       <c r="D1" s="7"/>
       <c r="E1" s="6" t="s">
         <v>1</v>
@@ -3278,84 +3257,84 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="27"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="24"/>
+      <c r="J2" s="28"/>
       <c r="K2" s="16">
         <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="27"/>
+      <c r="F3" s="31"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="24"/>
+      <c r="J3" s="28"/>
       <c r="K3" s="16">
         <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="24"/>
+      <c r="J4" s="28"/>
       <c r="K4" s="16">
         <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="24"/>
+      <c r="J5" s="28"/>
       <c r="K5" s="18">
         <f>SUM(K2:K4)</f>
         <v>0</v>
@@ -4053,11 +4032,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
       <c r="D1" s="7"/>
       <c r="E1" s="6" t="s">
         <v>1</v>
@@ -4070,84 +4049,84 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="27"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="24"/>
+      <c r="J2" s="28"/>
       <c r="K2" s="16">
         <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="27"/>
+      <c r="F3" s="31"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="24"/>
+      <c r="J3" s="28"/>
       <c r="K3" s="16">
         <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="24"/>
+      <c r="J4" s="28"/>
       <c r="K4" s="16">
         <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="24"/>
+      <c r="J5" s="28"/>
       <c r="K5" s="18">
         <f>SUM(K2:K4)</f>
         <v>2</v>
@@ -4869,11 +4848,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
       <c r="D1" s="7"/>
       <c r="E1" s="6" t="s">
         <v>1</v>
@@ -4886,84 +4865,84 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="27"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="24"/>
+      <c r="J2" s="28"/>
       <c r="K2" s="16">
         <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="27"/>
+      <c r="F3" s="31"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="24"/>
+      <c r="J3" s="28"/>
       <c r="K3" s="16">
         <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="24"/>
+      <c r="J4" s="28"/>
       <c r="K4" s="16">
         <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="24"/>
+      <c r="J5" s="28"/>
       <c r="K5" s="18">
         <f>SUM(K2:K4)</f>
         <v>3</v>
@@ -5699,11 +5678,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
       <c r="D1" s="7"/>
       <c r="E1" s="6" t="s">
         <v>1</v>
@@ -5716,84 +5695,84 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="27"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="24"/>
+      <c r="J2" s="28"/>
       <c r="K2" s="16">
         <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="27"/>
+      <c r="F3" s="31"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="24"/>
+      <c r="J3" s="28"/>
       <c r="K3" s="16">
         <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="24"/>
+      <c r="J4" s="28"/>
       <c r="K4" s="16">
         <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="24"/>
+      <c r="J5" s="28"/>
       <c r="K5" s="18">
         <f>SUM(K2:K4)</f>
         <v>0</v>
@@ -6491,11 +6470,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
       <c r="D1" s="7"/>
       <c r="E1" s="6" t="s">
         <v>1</v>
@@ -6508,84 +6487,84 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="27"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="24"/>
+      <c r="J2" s="28"/>
       <c r="K2" s="16">
         <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="27"/>
+      <c r="F3" s="31"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="24"/>
+      <c r="J3" s="28"/>
       <c r="K3" s="16">
         <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="24"/>
+      <c r="J4" s="28"/>
       <c r="K4" s="16">
         <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="24"/>
+      <c r="J5" s="28"/>
       <c r="K5" s="18">
         <f>SUM(K2:K4)</f>
         <v>0</v>
@@ -7284,11 +7263,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
       <c r="D1" s="7"/>
       <c r="E1" s="6" t="s">
         <v>1</v>
@@ -7301,84 +7280,84 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="27"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="24"/>
+      <c r="J2" s="28"/>
       <c r="K2" s="16">
         <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="27"/>
+      <c r="F3" s="31"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="24"/>
+      <c r="J3" s="28"/>
       <c r="K3" s="16">
         <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="24"/>
+      <c r="J4" s="28"/>
       <c r="K4" s="16">
         <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="24"/>
+      <c r="J5" s="28"/>
       <c r="K5" s="18">
         <f>SUM(K2:K4)</f>
         <v>30</v>
@@ -7835,23 +7814,21 @@
         <v>49</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E21" s="12">
         <v>46244</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G21" s="15">
         <v>1</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="I21" s="1"/>
       <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7866,23 +7843,21 @@
         <v>49</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E22" s="12">
         <v>46244</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="I22" s="1"/>
       <c r="J22" s="2"/>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7897,23 +7872,21 @@
         <v>49</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E23" s="12">
         <v>46244</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G23" s="15">
         <v>1</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="I23" s="1"/>
       <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7928,23 +7901,21 @@
         <v>49</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E24" s="12">
         <v>46244</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G24" s="15">
         <v>1</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="I24" s="1"/>
       <c r="J24" s="2"/>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7959,23 +7930,21 @@
         <v>49</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E25" s="12">
         <v>46244</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G25" s="15">
         <v>1</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="I25" s="1"/>
       <c r="J25" s="2"/>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8004,9 +7973,7 @@
       <c r="H26" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>81</v>
-      </c>
+      <c r="I26" s="2"/>
       <c r="J26" s="2"/>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8021,19 +7988,19 @@
         <v>49</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E27" s="12">
         <v>46244</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
@@ -8050,23 +8017,21 @@
         <v>49</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E28" s="12">
         <v>46244</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G28" s="15">
         <v>1</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="I28" s="21">
-        <v>46208</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="I28" s="21"/>
       <c r="J28" s="2"/>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8081,23 +8046,21 @@
         <v>20</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E29" s="12">
         <v>46244</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G29" s="15">
         <v>1</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>94</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="I29" s="2"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8105,20 +8068,20 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="E30" s="30">
+      <c r="D30" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E30" s="24">
         <v>46244</v>
       </c>
-      <c r="F30" s="31" t="s">
-        <v>98</v>
+      <c r="F30" s="25" t="s">
+        <v>94</v>
       </c>
       <c r="G30" s="15">
         <v>1</v>
@@ -8126,9 +8089,7 @@
       <c r="H30" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>97</v>
-      </c>
+      <c r="I30" s="2"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8143,23 +8104,21 @@
         <v>20</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E31" s="12">
         <v>46244</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="G31" s="15">
         <v>1</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>81</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="I31" s="2"/>
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8174,23 +8133,21 @@
         <v>20</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E32" s="12">
         <v>46244</v>
       </c>
       <c r="F32" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" s="15">
+        <v>1</v>
+      </c>
+      <c r="H32" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="G32" s="15">
-        <v>1</v>
-      </c>
-      <c r="H32" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="I32" s="2"/>
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8205,23 +8162,21 @@
         <v>20</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E33" s="12">
         <v>46244</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G33" s="15">
         <v>1</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>101</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="I33" s="2"/>
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8236,23 +8191,21 @@
         <v>20</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E34" s="12">
         <v>46244</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G34" s="15">
         <v>1</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>108</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8267,23 +8220,21 @@
         <v>20</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E35" s="12">
         <v>46244</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G35" s="15">
         <v>1</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I35" s="1" t="s">
         <v>108</v>
       </c>
+      <c r="I35" s="1"/>
       <c r="J35" s="1"/>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8298,23 +8249,21 @@
         <v>20</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E36" s="12">
         <v>46244</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G36" s="15">
         <v>1</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>108</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="I36" s="1"/>
       <c r="J36" s="1"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">

--- a/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Zoubiria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980581EE-C2EC-4807-9756-7781CE3F1335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1ED0705-755D-4775-AAD4-D5837D60E06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -453,27 +453,18 @@
     <t>NB(290/2026)</t>
   </si>
   <si>
-    <t>2023004016</t>
-  </si>
-  <si>
     <t>NB(167/2025)</t>
   </si>
   <si>
     <t>Boulariah med</t>
   </si>
   <si>
-    <t>2023004017</t>
-  </si>
-  <si>
     <t>Tamen sid ali</t>
   </si>
   <si>
     <t>NB(293/2026)</t>
   </si>
   <si>
-    <t>2023004018</t>
-  </si>
-  <si>
     <t>Lakli boudaya</t>
   </si>
   <si>
@@ -549,49 +540,58 @@
     <t>NB(117/2026)</t>
   </si>
   <si>
-    <t>2023004014</t>
-  </si>
-  <si>
     <t>Bensadat aissa</t>
   </si>
   <si>
     <t>NB(019/2026)</t>
   </si>
   <si>
-    <t>2023004015</t>
-  </si>
-  <si>
     <t>Bensadat boualem</t>
   </si>
   <si>
     <t>NB(020/2026)</t>
   </si>
   <si>
-    <t>2023004013</t>
-  </si>
-  <si>
     <t>Bensadat aek</t>
   </si>
   <si>
     <t>NB(021/2026)</t>
   </si>
   <si>
-    <t>2023004012</t>
-  </si>
-  <si>
     <t>Bensadat menouar</t>
   </si>
   <si>
     <t>NB(018/2026)</t>
   </si>
   <si>
-    <t>2023004011</t>
-  </si>
-  <si>
     <t>Tarfaoui aek</t>
   </si>
   <si>
     <t>NB(220/2026)</t>
+  </si>
+  <si>
+    <t>2026004011</t>
+  </si>
+  <si>
+    <t>2026004012</t>
+  </si>
+  <si>
+    <t>2026004013</t>
+  </si>
+  <si>
+    <t>2026004014</t>
+  </si>
+  <si>
+    <t>2026004015</t>
+  </si>
+  <si>
+    <t>2026004016</t>
+  </si>
+  <si>
+    <t>2026004017</t>
+  </si>
+  <si>
+    <t>2026004018</t>
   </si>
 </sst>
 </file>
@@ -7814,19 +7814,19 @@
         <v>49</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E21" s="12">
         <v>46244</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="G21" s="15">
         <v>1</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="2"/>
@@ -7843,19 +7843,19 @@
         <v>49</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E22" s="12">
         <v>46244</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="2"/>
@@ -7872,19 +7872,19 @@
         <v>49</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E23" s="12">
         <v>46244</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G23" s="15">
         <v>1</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="2"/>
@@ -7901,19 +7901,19 @@
         <v>49</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E24" s="12">
         <v>46244</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G24" s="15">
         <v>1</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="2"/>
@@ -7930,19 +7930,19 @@
         <v>49</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E25" s="12">
         <v>46244</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G25" s="15">
         <v>1</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="2"/>
@@ -7959,19 +7959,19 @@
         <v>49</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="E26" s="12">
         <v>46244</v>
       </c>
       <c r="F26" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="G26" s="15">
+        <v>1</v>
+      </c>
+      <c r="H26" s="20" t="s">
         <v>79</v>
-      </c>
-      <c r="G26" s="15">
-        <v>1</v>
-      </c>
-      <c r="H26" s="20" t="s">
-        <v>80</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
@@ -7988,19 +7988,19 @@
         <v>49</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="E27" s="12">
         <v>46244</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
@@ -8017,19 +8017,19 @@
         <v>49</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="E28" s="12">
         <v>46244</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G28" s="15">
         <v>1</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I28" s="21"/>
       <c r="J28" s="2"/>
@@ -8046,19 +8046,19 @@
         <v>20</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E29" s="12">
         <v>46244</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G29" s="15">
         <v>1</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="1"/>
@@ -8075,13 +8075,13 @@
         <v>20</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E30" s="24">
         <v>46244</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G30" s="15">
         <v>1</v>
@@ -8104,19 +8104,19 @@
         <v>20</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E31" s="12">
         <v>46244</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G31" s="15">
         <v>1</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="1"/>
@@ -8133,19 +8133,19 @@
         <v>20</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E32" s="12">
         <v>46244</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G32" s="15">
         <v>1</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="1"/>
@@ -8162,19 +8162,19 @@
         <v>20</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E33" s="12">
         <v>46244</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G33" s="15">
         <v>1</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I33" s="2"/>
       <c r="J33" s="1"/>
@@ -8191,19 +8191,19 @@
         <v>20</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E34" s="12">
         <v>46244</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G34" s="15">
         <v>1</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -8220,19 +8220,19 @@
         <v>20</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E35" s="12">
         <v>46244</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G35" s="15">
         <v>1</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -8249,19 +8249,19 @@
         <v>20</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E36" s="12">
         <v>46244</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G36" s="15">
         <v>1</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>

--- a/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Zoubiria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1ED0705-755D-4775-AAD4-D5837D60E06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76201A8C-6A69-453E-96BA-0C4BE3C0BB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="127">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -592,6 +592,12 @@
   </si>
   <si>
     <t>2026004018</t>
+  </si>
+  <si>
+    <t>130148</t>
+  </si>
+  <si>
+    <t>2026144266</t>
   </si>
 </sst>
 </file>
@@ -8271,11 +8277,21 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="19"/>
+      <c r="B37" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E37" s="12">
+        <v>46265</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="14">

--- a/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Zoubiria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76201A8C-6A69-453E-96BA-0C4BE3C0BB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E7D24B-BC5F-46D0-BC55-A78A83FDA09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2026" sheetId="12" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="JUIN 2026" sheetId="17" r:id="rId6"/>
     <sheet name="JUILLET 2026" sheetId="18" r:id="rId7"/>
     <sheet name="AOUT 2026" sheetId="19" r:id="rId8"/>
+    <sheet name="SEPTEMBRE 2026" sheetId="20" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'AOUT 2026'!$1:$6</definedName>
@@ -31,6 +32,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'JUIN 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'MAI 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'MARS 2026'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'SEPTEMBRE 2026'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="141">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -598,6 +600,59 @@
   </si>
   <si>
     <t>2026144266</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mois de SEPTEMBRE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
+  <si>
+    <t>NB(272/2026)</t>
+  </si>
+  <si>
+    <t>Djellal med</t>
+  </si>
+  <si>
+    <t>NB(109/2026)</t>
+  </si>
+  <si>
+    <t>Amraoui benyoucef</t>
+  </si>
+  <si>
+    <t>Amraoui khadidja</t>
+  </si>
+  <si>
+    <t>Ammad ali</t>
+  </si>
+  <si>
+    <t>NB(362/2026)</t>
+  </si>
+  <si>
+    <t>Berrached aek</t>
+  </si>
+  <si>
+    <t>NB(291/2026)</t>
+  </si>
+  <si>
+    <t>Ziouer khaled</t>
+  </si>
+  <si>
+    <t>NB(203/2026)</t>
+  </si>
+  <si>
+    <t>Djaoui brahim</t>
+  </si>
+  <si>
+    <t>NB(332/2026)</t>
   </si>
 </sst>
 </file>
@@ -1326,6 +1381,61 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19052</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Connecteur droit 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CDF7FE1-2A6F-48D8-B531-A3D721FB84E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="609602" y="7277100"/>
+          <a:ext cx="4076698" cy="1638300"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -8419,4 +8529,885 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F0853CF-2220-448E-A89E-134DF0870589}">
+  <dimension ref="A1:K46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="6"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="31"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="28"/>
+      <c r="K2" s="16">
+        <f>SUMIF(F7:F36,"Elimination*",G7:G36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="31"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="28"/>
+      <c r="K3" s="16">
+        <f>SUMIF(F7:F36,"NB*",G7:G36)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="28"/>
+      <c r="K4" s="16">
+        <f>SUMIF(F7:F36,"Ve*",G7:G36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="28"/>
+      <c r="K5" s="18">
+        <f>SUM(K2:K4)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10">
+        <v>13</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="10">
+        <v>2026003649</v>
+      </c>
+      <c r="E7" s="12">
+        <v>46272</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G7" s="15">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14">
+        <f t="shared" ref="A8:A46" si="0">+A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="10">
+        <v>13</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="10">
+        <v>2026004091</v>
+      </c>
+      <c r="E8" s="12">
+        <v>46272</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="G8" s="15">
+        <v>1</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B9" s="10">
+        <v>13</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="10">
+        <v>2026004092</v>
+      </c>
+      <c r="E9" s="12">
+        <v>46272</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="G9" s="15">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="10">
+        <v>13</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="10">
+        <v>2026004093</v>
+      </c>
+      <c r="E10" s="12">
+        <v>46272</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="G10" s="15">
+        <v>1</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="10">
+        <v>13</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="10">
+        <v>2026004094</v>
+      </c>
+      <c r="E11" s="12">
+        <v>46272</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="G11" s="15">
+        <v>1</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B12" s="10">
+        <v>13</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="10">
+        <v>2026004095</v>
+      </c>
+      <c r="E12" s="12">
+        <v>46272</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="G12" s="15">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B13" s="10">
+        <v>13</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="10">
+        <v>2026004098</v>
+      </c>
+      <c r="E13" s="12">
+        <v>46272</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="G13" s="15">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="15">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="15">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="15">
+        <v>1</v>
+      </c>
+      <c r="H17" s="20"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="15">
+        <v>1</v>
+      </c>
+      <c r="H18" s="20"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="15">
+        <v>1</v>
+      </c>
+      <c r="H19" s="20"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="15">
+        <v>1</v>
+      </c>
+      <c r="H20" s="20"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="15">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="15">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="14">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="15">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="15">
+        <v>1</v>
+      </c>
+      <c r="H26" s="20"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="14">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="20"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="15">
+        <v>1</v>
+      </c>
+      <c r="H28" s="20"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="15">
+        <v>1</v>
+      </c>
+      <c r="H29" s="20"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B30" s="22"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="15">
+        <v>1</v>
+      </c>
+      <c r="H30" s="20"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="20"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="15">
+        <v>1</v>
+      </c>
+      <c r="H32" s="20"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="15">
+        <v>1</v>
+      </c>
+      <c r="H33" s="20"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="9"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="15">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B35" s="9"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="15">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="15">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="14">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="19"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="14">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B38" s="9"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="19"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="14">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="19"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="14">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="19"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="14">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="19"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="14">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="9"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="19"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="14">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="19"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="14">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="19"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="14">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B45" s="9"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="19"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="14">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="19"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H12">
+    <sortCondition ref="E7:E12"/>
+    <sortCondition ref="D7:D12"/>
+  </sortState>
+  <mergeCells count="11">
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>